--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ35"/>
+  <dimension ref="A1:AQ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5024,10 +5024,8 @@
           <t>6490,6060,6190,5840,5710</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Y32" t="n">
+        <v>4</v>
       </c>
       <c r="Z32" t="n">
         <v>271000</v>
@@ -5169,10 +5167,8 @@
           <t>6700,8000,7600,7220,8580</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y33" t="n">
+        <v>2</v>
       </c>
       <c r="Z33" t="n">
         <v>24000</v>
@@ -5314,10 +5310,8 @@
           <t>2100,2300,2990,3100,3430</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
+      <c r="Y34" t="n">
+        <v>-3</v>
       </c>
       <c r="Z34" t="n">
         <v>88000</v>
@@ -5459,10 +5453,8 @@
           <t>5070,5210,5230,6790,7570</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>-4</t>
-        </is>
+      <c r="Y35" t="n">
+        <v>-4</v>
       </c>
       <c r="Z35" t="n">
         <v>-59000</v>
@@ -5514,6 +5506,743 @@
       <c r="AQ35" t="inlineStr">
         <is>
           <t>호남 반도체 클러스터 관련 기대감 속 하락세 지속. 외인 매집 및 투자위험 경고 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:01</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>336260</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>57</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="L36" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>51800</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>+18.13%</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>2511374</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>129586984575</v>
+      </c>
+      <c r="R36" t="n">
+        <v>118.45</v>
+      </c>
+      <c r="S36" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="U36" t="n">
+        <v>160</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>45150,44350,38700,39000,43850</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z36" t="n">
+        <v>176000</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>44000</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>-48.11</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>345.88</v>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AE36" t="n">
+        <v>34000</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>48.82</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="n">
+        <v>-31.92</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>-1623</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>4491</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>108900</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>18230</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>33926</v>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>공매도 세력에 대한 기대감 및 6~7만원 구간 매물벽 약세 전망. 단기 급등 후 소강 상태 진입 및 4만원 재진입 가능성 언급. 공급 계약 발표 후 급등 사례 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:01</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>57</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="L37" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>83650</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>+5.62%</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>2063900</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>170941399250</v>
+      </c>
+      <c r="R37" t="n">
+        <v>163.72</v>
+      </c>
+      <c r="S37" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="T37" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="U37" t="n">
+        <v>149</v>
+      </c>
+      <c r="V37" t="n">
+        <v>9</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>82500,81400,76600,79200,79200</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z37" t="n">
+        <v>146000</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>136.43</v>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="n">
+        <v>633.71</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>132</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>12156</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>139200</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>57000</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>535829</v>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>대규모 가스복합화력발전 투자 확정 및 하반기 본격 수주 기대감. 기술력 입증 및 10만원 돌파 전망. 원전주 전반적인 상승세 속에서 상대적 우위 확인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:01</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>3</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LG전자</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>066570</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>57</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="L38" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>215500</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>+6.95%</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>1292221</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>284539442750</v>
+      </c>
+      <c r="R38" t="n">
+        <v>143.64</v>
+      </c>
+      <c r="S38" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="T38" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U38" t="n">
+        <v>404</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>216500,206500,200500,199700,201500</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z38" t="n">
+        <v>353000</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>124000</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>130.9</v>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE38" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>5321</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>132659</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>438000</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>74700</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>351016</v>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>로봇 사업 관련 기술력 부각 및 60년 기술 노하우 강조. 외인·기관 매수세 유입에 따른 상승 기대감 표출.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:01</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>57</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="L39" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>1747000</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>+6.07%</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>1540461</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2682641606500</v>
+      </c>
+      <c r="R39" t="n">
+        <v>123.28</v>
+      </c>
+      <c r="S39" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="U39" t="n">
+        <v>794</v>
+      </c>
+      <c r="V39" t="n">
+        <v>65</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>1674000,1693000,1613000,1596000,1647000</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z39" t="n">
+        <v>330000</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>138000</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="AE39" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>-27.58</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="n">
+        <v>29.63</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>274000</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>12761702</v>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>외국인 및 기관 쌍끌이 매수세 유입에 따른 상승 추세 가속화 전망. 자사주 매입 기대감 및 메모리 재고 부족 뉴스 언급. 200만원 터치 및 급등 가능성 제시.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:01</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>5</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>스카이랩스</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>386380</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>57</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="L40" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>27600</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>+17.45%</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>25587704</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>665867321400</v>
+      </c>
+      <c r="R40" t="n">
+        <v>97.67</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>649</v>
+      </c>
+      <c r="V40" t="n">
+        <v>2</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z40" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>999</v>
+      </c>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>29600</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>5178</v>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>CART 혈압계 관련 뉴스 확인 및 거래량 증가에 따른 상승 기대감. 주포의 움직임 및 종가 상한가 가능성 언급. '세계 1위, 최초' 등의 수식어 활용.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ40"/>
+  <dimension ref="A1:AQ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5596,10 +5596,8 @@
           <t>45150,44350,38700,39000,43850</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y36" t="n">
+        <v>5</v>
       </c>
       <c r="Z36" t="n">
         <v>176000</v>
@@ -5745,10 +5743,8 @@
           <t>82500,81400,76600,79200,79200</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y37" t="n">
+        <v>6</v>
       </c>
       <c r="Z37" t="n">
         <v>146000</v>
@@ -5894,10 +5890,8 @@
           <t>216500,206500,200500,199700,201500</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y38" t="n">
+        <v>5</v>
       </c>
       <c r="Z38" t="n">
         <v>353000</v>
@@ -6043,10 +6037,8 @@
           <t>1674000,1693000,1613000,1596000,1647000</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y39" t="n">
+        <v>7</v>
       </c>
       <c r="Z39" t="n">
         <v>330000</v>
@@ -6188,10 +6180,8 @@
         <v>1</v>
       </c>
       <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y40" t="n">
+        <v>3</v>
       </c>
       <c r="Z40" t="n">
         <v>-9000</v>
@@ -6243,6 +6233,453 @@
       <c r="AQ40" t="inlineStr">
         <is>
           <t>CART 혈압계 관련 뉴스 확인 및 거래량 증가에 따른 상승 기대감. 주포의 움직임 및 종가 상한가 가능성 언급. '세계 1위, 최초' 등의 수식어 활용.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-07 15:03</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>삼미금속</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>012210</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>75</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L41" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>10140</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>+21.44%</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>16301473</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>163981641855</v>
+      </c>
+      <c r="R41" t="n">
+        <v>87.48</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="T41" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="U41" t="n">
+        <v>158</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>8800,8460,8260,8340,8350</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z41" t="n">
+        <v>54000</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-937000</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>20850</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>4020</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>2337</v>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>삼미금속, 미국 초대형 가스발전 관련 뉴스에도 불구하고 수급 불안정으로 인한 하락 우려. 장난질 심한 흐름 속에 개미 물량 집중.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-07 15:03</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>매드업</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0039P0</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="n">
+        <v>75</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L42" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>9360</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>+14.43%</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>9969172</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>95198577230</v>
+      </c>
+      <c r="R42" t="n">
+        <v>87.62</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="U42" t="n">
+        <v>143</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>7600,9180,9260,7830,8180</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z42" t="n">
+        <v>146000</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>127.93</v>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE42" t="n">
+        <v>14500</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>-29.93</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>614</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>2059</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>22500</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>4560</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1760</v>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>매드업, AI 영상 기술력 기반 매출 기대감 속 프로그램 매수세 유입. 10,000원 안착 시 신고가 경신 전망. 계단식 하락 및 희망고문 논란.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-07 15:03</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>3</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>75</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L43" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>269000</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>+5.28%</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>15068345</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>4024423293750</v>
+      </c>
+      <c r="R43" t="n">
+        <v>125.37</v>
+      </c>
+      <c r="S43" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U43" t="n">
+        <v>140</v>
+      </c>
+      <c r="V43" t="n">
+        <v>100</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>260000,261000,250500,250000,255500</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z43" t="n">
+        <v>1534000</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1290000</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="AE43" t="n">
+        <v>450000</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>-40.72</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="n">
+        <v>40.98</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>69600</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>15726489</v>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>삼성전자, 27만원 돌파 기대감 속 단기 위험 구간 진입. 외인·기관 매물 출회 추측. 반도체 업황 기대감 존재.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ43"/>
+  <dimension ref="A1:AQ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6323,10 +6323,8 @@
           <t>8800,8460,8260,8340,8350</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y41" t="n">
+        <v>2</v>
       </c>
       <c r="Z41" t="n">
         <v>54000</v>
@@ -6472,10 +6470,8 @@
           <t>7600,9180,9260,7830,8180</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y42" t="n">
+        <v>3</v>
       </c>
       <c r="Z42" t="n">
         <v>146000</v>
@@ -6621,10 +6617,8 @@
           <t>260000,261000,250500,250000,255500</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y43" t="n">
+        <v>5</v>
       </c>
       <c r="Z43" t="n">
         <v>1534000</v>
@@ -6680,6 +6674,743 @@
       <c r="AQ43" t="inlineStr">
         <is>
           <t>삼성전자, 27만원 돌파 기대감 속 단기 위험 구간 진입. 외인·기관 매물 출회 추측. 반도체 업황 기대감 존재.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:01</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>42</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>46</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="n">
+        <v>21200</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>+15.15%</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>18857692</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>379532450640</v>
+      </c>
+      <c r="R44" t="n">
+        <v>133.18</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U44" t="n">
+        <v>233</v>
+      </c>
+      <c r="V44" t="n">
+        <v>11</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>16820,16280,16750,16850,18410</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z44" t="n">
+        <v>256000</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>207000</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>-14.26</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>266.54</v>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE44" t="n">
+        <v>22000</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>-8.859999999999999</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="n">
+        <v>-9.66</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>-2195</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>8148</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>40350</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>3320</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>87112</v>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>원전 사업 신사업 재료와 미국 원전 건설 수주 기대감으로 인한 주가 급등.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:01</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>42</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>46</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="n">
+        <v>92500</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>+5.23%</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>3748103</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>344442732400</v>
+      </c>
+      <c r="R45" t="n">
+        <v>142.25</v>
+      </c>
+      <c r="S45" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>298</v>
+      </c>
+      <c r="V45" t="n">
+        <v>10</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>81400,76600,79200,79200,87900</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z45" t="n">
+        <v>-222000</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>267000</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>136.43</v>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="n">
+        <v>700.76</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>132</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>12156</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>139200</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>57000</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>592519</v>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>원전 관련 이슈 및 미국 원전 투자 재료에 기반한 주가 상승 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:01</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>3</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>빛과전자</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>069540</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>42</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>46</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="n">
+        <v>3640</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>+30.00%</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>41277307</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>141530167503</v>
+      </c>
+      <c r="R46" t="n">
+        <v>94.62</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="T46" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="U46" t="n">
+        <v>100</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>2840,2765,2660,2715,2800</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z46" t="n">
+        <v>1255000</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>-17.45</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="n">
+        <v>-9.58</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>-380</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>947</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>8100</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>592</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>4102</v>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>AI 데이터센터 국산화 사업 선정 및 광통신 상용화 뉴스를 통한 급등세.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:01</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>4</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>현대약품</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>004310</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>42</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>46</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="n">
+        <v>10350</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>+22.92%</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>26450402</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>263450780000</v>
+      </c>
+      <c r="R47" t="n">
+        <v>95.14</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U47" t="n">
+        <v>172</v>
+      </c>
+      <c r="V47" t="n">
+        <v>6</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>8290,7570,7680,7950,8420</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z47" t="n">
+        <v>57000</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>15960</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>3312</v>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>미프진 관련 정부 정책 구체화 소식과 함께 낙태약 허가 기대감으로 인한 주가 상승세.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:01</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>5</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>한전기술</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>052690</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>42</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>46</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="n">
+        <v>140200</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>+14.64%</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>1214612</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>166435026500</v>
+      </c>
+      <c r="R48" t="n">
+        <v>112.37</v>
+      </c>
+      <c r="S48" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="U48" t="n">
+        <v>107</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>110500,105800,107400,107600,122300</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="Z48" t="n">
+        <v>-11000</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>64000</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>33.54</v>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE48" t="n">
+        <v>160000</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>-11.06</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="n">
+        <v>62.76</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>2234</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>16428</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>198000</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>77100</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>53584</v>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>260조 규모의 미국 원전 사업 수주 기대감과 함께, 단기 고점 및 재료 소멸 가능성 언급. 외인 매도세 포착.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ48"/>
+  <dimension ref="A1:AQ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6764,10 +6764,8 @@
           <t>16820,16280,16750,16850,18410</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y44" t="n">
+        <v>7</v>
       </c>
       <c r="Z44" t="n">
         <v>256000</v>
@@ -6913,10 +6911,8 @@
           <t>81400,76600,79200,79200,87900</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y45" t="n">
+        <v>5</v>
       </c>
       <c r="Z45" t="n">
         <v>-222000</v>
@@ -7062,10 +7058,8 @@
           <t>2840,2765,2660,2715,2800</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="Y46" t="n">
+        <v>9</v>
       </c>
       <c r="Z46" t="n">
         <v>1255000</v>
@@ -7207,10 +7201,8 @@
           <t>8290,7570,7680,7950,8420</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y47" t="n">
+        <v>3</v>
       </c>
       <c r="Z47" t="n">
         <v>57000</v>
@@ -7352,10 +7344,8 @@
           <t>110500,105800,107400,107600,122300</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
+      <c r="Y48" t="n">
+        <v>-3</v>
       </c>
       <c r="Z48" t="n">
         <v>-11000</v>
@@ -7411,6 +7401,602 @@
       <c r="AQ48" t="inlineStr">
         <is>
           <t>260조 규모의 미국 원전 사업 수주 기대감과 함께, 단기 고점 및 재료 소멸 가능성 언급. 외인 매도세 포착.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-08 15:03</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>우리기술</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>032820</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>26</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="L49" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="n">
+        <v>11890</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>+8.88%</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>12556654</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>150213954800</v>
+      </c>
+      <c r="R49" t="n">
+        <v>107.08</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="T49" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="U49" t="n">
+        <v>150</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>10750,10620,10500,10630,10920</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z49" t="n">
+        <v>-507000</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>16000</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>21.94</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>123.87</v>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="n">
+        <v>2378</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>755</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>30200</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>3540</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>20544</v>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>미국 원전 8기 관련 70% 계약 기대감, 프랑스와의 원자력 협정 언급. 14000원 돌파 및 이번 달, 내일 상한가 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-08 15:03</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>26</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="L50" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="n">
+        <v>1800500</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>+0.98%</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>3702589</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>6836829822500</v>
+      </c>
+      <c r="R50" t="n">
+        <v>107.99</v>
+      </c>
+      <c r="S50" t="n">
+        <v>50.63</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="U50" t="n">
+        <v>318</v>
+      </c>
+      <c r="V50" t="n">
+        <v>66</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>1693000,1613000,1596000,1647000,1783000</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z50" t="n">
+        <v>57000</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>202000</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE50" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>-22.17</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>274000</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>13152515</v>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>SK하이닉스 200만 돌파 기대감 및 외인/기관 대량 매수세 유입. 데이터센터 수요 증가 및 마이크론 주가 상승 영향. 주가 급등 가능성 및 개인 매도세 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-08 15:03</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>3</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>26</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="L51" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="n">
+        <v>270500</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>+0.19%</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>19862294</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>5466238623750</v>
+      </c>
+      <c r="R51" t="n">
+        <v>106.58</v>
+      </c>
+      <c r="S51" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="U51" t="n">
+        <v>474</v>
+      </c>
+      <c r="V51" t="n">
+        <v>101</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>261000,250500,250000,255500,270000</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="Z51" t="n">
+        <v>1925000</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>862000</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE51" t="n">
+        <v>400000</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>-32.12</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="n">
+        <v>41.21</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>69600</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>15814184</v>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>삼성전자 주가 급등 후 외인/기관 순매수세 유입. 28만 매물대 돌파 시도 및 유가 상승, 금리 인상 우려 혼재. 정치적 이슈 관련 언급 다수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-08 15:03</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>4</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>금호건설</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>002990</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>26</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="L52" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="n">
+        <v>15630</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>-2.98%</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>5689279</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>90340988585</v>
+      </c>
+      <c r="R52" t="n">
+        <v>85.28</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>190</v>
+      </c>
+      <c r="V52" t="n">
+        <v>49</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>16500,17100,16510,16090,16110</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z52" t="n">
+        <v>-113000</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>30.01</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>405.51</v>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE52" t="n">
+        <v>5600</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>175</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>1715</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>6841</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>19380</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>3200</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>5824</v>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>미래 시점 주가 언급 및 건설주 상승세 동반. 30조대 가스복합발전소, 반도체 투자 관련 언급. 주가 급락 및 불확실성 혼재.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ52"/>
+  <dimension ref="A1:AQ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7491,10 +7491,8 @@
           <t>10750,10620,10500,10630,10920</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Y49" t="n">
+        <v>4</v>
       </c>
       <c r="Z49" t="n">
         <v>-507000</v>
@@ -7640,10 +7638,8 @@
           <t>1693000,1613000,1596000,1647000,1783000</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y50" t="n">
+        <v>3</v>
       </c>
       <c r="Z50" t="n">
         <v>57000</v>
@@ -7789,10 +7785,8 @@
           <t>261000,250500,250000,255500,270000</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="Y51" t="n">
+        <v>-1</v>
       </c>
       <c r="Z51" t="n">
         <v>1925000</v>
@@ -7938,10 +7932,8 @@
           <t>16500,17100,16510,16090,16110</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y52" t="n">
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
         <v>-113000</v>
@@ -7997,6 +7989,739 @@
       <c r="AQ52" t="inlineStr">
         <is>
           <t>미래 시점 주가 언급 및 건설주 상승세 동반. 30조대 가스복합발전소, 반도체 투자 관련 언급. 주가 급락 및 불확실성 혼재.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-08 15:11</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>서산</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>079650</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>26</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="L53" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="n">
+        <v>7580</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>+12.97%</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>20039282</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>153289146355</v>
+      </c>
+      <c r="R53" t="n">
+        <v>94.83</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="T53" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>203</v>
+      </c>
+      <c r="V53" t="n">
+        <v>7</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>5230,6790,7570,6730,6710</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z53" t="n">
+        <v>44000</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="n">
+        <v>-154.69</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>-49</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>3495</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>10300</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>952</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>1516</v>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>레미콘 총파업 관련 독점 수혜 기대감 및 외국인 매수세 유입으로 급등. 7연상 재도전 가능성 제시.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-08 15:11</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>한국전력</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>015760</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>26</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="L54" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="n">
+        <v>34200</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>+4.43%</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>3396874</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>115865718300</v>
+      </c>
+      <c r="R54" t="n">
+        <v>202.45</v>
+      </c>
+      <c r="S54" t="n">
+        <v>52.78</v>
+      </c>
+      <c r="T54" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="U54" t="n">
+        <v>123</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>32350,31250,32450,32150,32750</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z54" t="n">
+        <v>344000</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>275000</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>406.43</v>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE54" t="n">
+        <v>41000</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>-17.44</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>13311</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>75035</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>69500</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>30400</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>219552</v>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>미국 원전 사업 투자 및 웨스팅하우스 지분 인수 기대감으로 주가 상승. 공매도 물량 부담 속 10만 원 돌파 가능성 제시.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-08 15:11</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>3</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>스카이랩스</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>386380</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>26</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="L55" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="n">
+        <v>32600</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>+6.71%</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>30821991</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1083278531050</v>
+      </c>
+      <c r="R55" t="n">
+        <v>90.94</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U55" t="n">
+        <v>794</v>
+      </c>
+      <c r="V55" t="n">
+        <v>3</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>23500,30550</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z55" t="n">
+        <v>-51000</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>999</v>
+      </c>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>39350</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>6116</v>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>주포의 매집 및 10만 원 돌파 기대감 형성. 상승 후 장시간 횡보하며 급등 가능성 시사.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-08 15:11</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>4</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>JW신약</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>067290</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>26</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="L56" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="n">
+        <v>3840</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>+7.26%</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>72167601</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>284493743865</v>
+      </c>
+      <c r="R56" t="n">
+        <v>94.68000000000001</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="U56" t="n">
+        <v>190</v>
+      </c>
+      <c r="V56" t="n">
+        <v>7</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>2990,3100,3430,3265,3580</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="Z56" t="n">
+        <v>-436000</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>43</v>
+      </c>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr"/>
+      <c r="AJ56" t="n">
+        <v>13.76</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>279</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>729</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>4335</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>1246</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>2152</v>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>거래량 증가 속 횡보하며 계단식 하락세 지속. 4천 원 이탈 시 추가 하락 가능성 우려.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-08 15:11</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>5</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>26</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="L57" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="n">
+        <v>13710</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>+1.78%</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>16165731</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>227504423075</v>
+      </c>
+      <c r="R57" t="n">
+        <v>91.31</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="U57" t="n">
+        <v>155</v>
+      </c>
+      <c r="V57" t="n">
+        <v>10</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>13310,13570,12850,13010,13470</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z57" t="n">
+        <v>-103000</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>27000</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>-27.86</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>155.22</v>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr"/>
+      <c r="AJ57" t="n">
+        <v>-56.65</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>27.92</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>-242</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>491</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>31500</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>1252</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>21317</v>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>Texas 소식 및 광통신 관련 호재로 인한 상승 기대감. 14000원 돌파 및 15000원, 17510원 목표가 제시. 공매도 물량 부담.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ57"/>
+  <dimension ref="A1:AQ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8079,10 +8079,8 @@
           <t>5230,6790,7570,6730,6710</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="Y53" t="n">
+        <v>9</v>
       </c>
       <c r="Z53" t="n">
         <v>44000</v>
@@ -8224,10 +8222,8 @@
           <t>32350,31250,32450,32150,32750</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y54" t="n">
+        <v>7</v>
       </c>
       <c r="Z54" t="n">
         <v>344000</v>
@@ -8373,10 +8369,8 @@
           <t>23500,30550</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y55" t="n">
+        <v>8</v>
       </c>
       <c r="Z55" t="n">
         <v>-51000</v>
@@ -8518,10 +8512,8 @@
           <t>2990,3100,3430,3265,3580</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="Y56" t="n">
+        <v>-1</v>
       </c>
       <c r="Z56" t="n">
         <v>-436000</v>
@@ -8663,10 +8655,8 @@
           <t>13310,13570,12850,13010,13470</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y57" t="n">
+        <v>6</v>
       </c>
       <c r="Z57" t="n">
         <v>-103000</v>
@@ -8722,6 +8712,747 @@
       <c r="AQ57" t="inlineStr">
         <is>
           <t>Texas 소식 및 광통신 관련 호재로 인한 상승 기대감. 14000원 돌파 및 15000원, 17510원 목표가 제시. 공매도 물량 부담.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-09 12:02</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>페니트리움바이오</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>187660</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>61</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L58" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="n">
+        <v>7420</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>+29.95%</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>4359834</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>29442081335</v>
+      </c>
+      <c r="R58" t="n">
+        <v>113.04</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="T58" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="U58" t="n">
+        <v>211</v>
+      </c>
+      <c r="V58" t="n">
+        <v>3</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>4760,5100,5850,6470,5710</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z58" t="n">
+        <v>164000</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>-118.31</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>330.36</v>
+      </c>
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr"/>
+      <c r="AJ58" t="n">
+        <v>-17.02</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>48.82</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>-436</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>152</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>21500</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>2300</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>4746</v>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>미 FDA 2A상 승인 및 암세포 사멸 관련 역대급 뉴스로 10연상 등 강한 상승 기대. 다락손라십 대비 우수하며, 외국인 매수세 유입 확인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-09 12:02</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>2</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>61</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L59" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="n">
+        <v>92400</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>+3.24%</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>2496844</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>232286482100</v>
+      </c>
+      <c r="R59" t="n">
+        <v>124.27</v>
+      </c>
+      <c r="S59" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="T59" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="U59" t="n">
+        <v>277</v>
+      </c>
+      <c r="V59" t="n">
+        <v>11</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>76600,79200,79200,87900,89500</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z59" t="n">
+        <v>104000</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>26000</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>136.43</v>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr"/>
+      <c r="AJ59" t="n">
+        <v>700</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>132</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>12156</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>139200</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>57000</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>591878</v>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>미국 원전 사업 참여 및 SMR 기술 관련 기대감. 프랑스와의 원자력 협력 뉴스 기반 상승 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-09 12:02</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>3</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>61</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L60" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="n">
+        <v>1863000</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>+3.90%</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>1930404</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>3558039272000</v>
+      </c>
+      <c r="R60" t="n">
+        <v>118.79</v>
+      </c>
+      <c r="S60" t="n">
+        <v>50.66</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U60" t="n">
+        <v>796</v>
+      </c>
+      <c r="V60" t="n">
+        <v>67</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>1613000,1596000,1647000,1783000,1793000</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z60" t="n">
+        <v>53000</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>37000</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE60" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>-21.52</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr"/>
+      <c r="AJ60" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>277000</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>13609073</v>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>외인 및 기관 매수세 유입과 함께 190~200만원 돌파 기대감 형성. 자사주 매입 및 리밸런싱 완료 추측. 추석 전 상승 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-09 12:02</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>4</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>한국전력</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>015760</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>61</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L61" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="n">
+        <v>34300</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>+0.59%</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>1712348</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>59355119200</v>
+      </c>
+      <c r="R61" t="n">
+        <v>124.81</v>
+      </c>
+      <c r="S61" t="n">
+        <v>52.62</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>93</v>
+      </c>
+      <c r="V61" t="n">
+        <v>2</v>
+      </c>
+      <c r="W61" t="n">
+        <v>1</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>31250,32450,32150,32750,34100</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z61" t="n">
+        <v>-78000</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>61000</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>406.43</v>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="AE61" t="n">
+        <v>48000</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>-27.6</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>13311</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>75035</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>69500</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>30400</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>220194</v>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>미국 원전 협력 및 한국전력 발전 5사 통합 긍정적 이슈 언급. 25조 선납매 및 숏스퀴즈 가능성 제기하며 45000원 목표가 제시.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-09 12:02</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>5</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" t="n">
+        <v>61</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L62" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="n">
+        <v>273250</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>+1.39%</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>8491172</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>2308305506250</v>
+      </c>
+      <c r="R62" t="n">
+        <v>87.09</v>
+      </c>
+      <c r="S62" t="n">
+        <v>46.85</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="U62" t="n">
+        <v>475</v>
+      </c>
+      <c r="V62" t="n">
+        <v>102</v>
+      </c>
+      <c r="W62" t="n">
+        <v>1</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>250500,250000,255500,270000,269500</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z62" t="n">
+        <v>-301000</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>176000</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE62" t="n">
+        <v>400000</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>-32.62</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="n">
+        <v>41.63</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>70000</v>
+      </c>
+      <c r="AP62" t="n">
+        <v>15974956</v>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>SK하이닉스와의 비교 언급이 많으며, 60일선 돌파 임박 및 28만원 박스권 유지 전망. 자사주 발표 및 주주환원 정책에 대한 언급 존재.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ62"/>
+  <dimension ref="A1:AQ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8802,10 +8802,8 @@
           <t>4760,5100,5850,6470,5710</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="Y58" t="n">
+        <v>9</v>
       </c>
       <c r="Z58" t="n">
         <v>164000</v>
@@ -8947,10 +8945,8 @@
           <t>76600,79200,79200,87900,89500</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y59" t="n">
+        <v>5</v>
       </c>
       <c r="Z59" t="n">
         <v>104000</v>
@@ -9096,10 +9092,8 @@
           <t>1613000,1596000,1647000,1783000,1793000</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y60" t="n">
+        <v>6</v>
       </c>
       <c r="Z60" t="n">
         <v>53000</v>
@@ -9245,10 +9239,8 @@
           <t>31250,32450,32150,32750,34100</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y61" t="n">
+        <v>6</v>
       </c>
       <c r="Z61" t="n">
         <v>-78000</v>
@@ -9394,10 +9386,8 @@
           <t>250500,250000,255500,270000,269500</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y62" t="n">
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
         <v>-301000</v>
@@ -9453,6 +9443,739 @@
       <c r="AQ62" t="inlineStr">
         <is>
           <t>SK하이닉스와의 비교 언급이 많으며, 60일선 돌파 임박 및 28만원 박스권 유지 전망. 자사주 발표 및 주주환원 정책에 대한 언급 존재.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:01</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>54</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L63" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="n">
+        <v>14950</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>+9.12%</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>29041997</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>437313985410</v>
+      </c>
+      <c r="R63" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="S63" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="T63" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="U63" t="n">
+        <v>273</v>
+      </c>
+      <c r="V63" t="n">
+        <v>11</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>13570,12850,13010,13470,13700</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z63" t="n">
+        <v>590000</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>20000</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>-27.86</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>155.22</v>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr"/>
+      <c r="AJ63" t="n">
+        <v>-61.78</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>30.45</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>-242</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>491</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>31500</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>1252</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>23245</v>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>단기 박스권 돌파 및 불기둥 형성, 2만 목표 상향 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:01</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>삼미금속</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>012210</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>54</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L64" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="n">
+        <v>13030</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>+29.91%</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>19567135</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>233282725825</v>
+      </c>
+      <c r="R64" t="n">
+        <v>90.48</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="T64" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="U64" t="n">
+        <v>199</v>
+      </c>
+      <c r="V64" t="n">
+        <v>3</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>8260,8340,8350,10200,10030</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z64" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>19000</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr"/>
+      <c r="AJ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>20850</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>4020</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>3004</v>
+      </c>
+      <c r="AQ64" t="inlineStr">
+        <is>
+          <t>미국 증시 SMR 관련주 폭등에 따른 기대감, 품절주 특성 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:01</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>3</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>강동씨앤엘</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>198440</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>54</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L65" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="n">
+        <v>2035</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>+5.88%</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>8614707</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>17571997184</v>
+      </c>
+      <c r="R65" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="T65" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>120</v>
+      </c>
+      <c r="V65" t="n">
+        <v>2</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>2135,2095,1963,1970,1922</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z65" t="n">
+        <v>154000</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>-6.81</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>227.6</v>
+      </c>
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr"/>
+      <c r="AJ65" t="n">
+        <v>-12.26</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>-166</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>2206</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>2930</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>910</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>1240</v>
+      </c>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>반도체 클러스터 관련 논의 및 주포 동향 주시, 주가 상승 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:01</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>4</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>스카이랩스</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>386380</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" t="n">
+        <v>54</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L66" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="n">
+        <v>30750</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>+3.36%</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>16661723</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>522764760150</v>
+      </c>
+      <c r="R66" t="n">
+        <v>84.02</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="U66" t="n">
+        <v>714</v>
+      </c>
+      <c r="V66" t="n">
+        <v>4</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>23500,30550,29750</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z66" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>999</v>
+      </c>
+      <c r="AD66" t="inlineStr"/>
+      <c r="AE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr"/>
+      <c r="AJ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>39350</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>5769</v>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>혈압계 관련 뉴스 및 유럽 진출 소식, 주가 반등 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:01</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>5</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>써니전자</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>004770</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>54</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L67" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="n">
+        <v>2185</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>+1.16%</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>18253359</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>44640050294</v>
+      </c>
+      <c r="R67" t="n">
+        <v>88.45999999999999</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T67" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="U67" t="n">
+        <v>185</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1</v>
+      </c>
+      <c r="W67" t="n">
+        <v>1</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>1865,2085,2185,2025,2160</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z67" t="n">
+        <v>22000</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr"/>
+      <c r="AJ67" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>2295</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>2705</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>1418</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>776</v>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>지분 싸움 및 신규 대주주 관련 논의, 단기 목표가 언급.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ67"/>
+  <dimension ref="A1:AQ72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9533,10 +9533,8 @@
           <t>13570,12850,13010,13470,13700</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y63" t="n">
+        <v>7</v>
       </c>
       <c r="Z63" t="n">
         <v>590000</v>
@@ -9682,10 +9680,8 @@
           <t>8260,8340,8350,10200,10030</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y64" t="n">
+        <v>7</v>
       </c>
       <c r="Z64" t="n">
         <v>10000</v>
@@ -9831,10 +9827,8 @@
           <t>2135,2095,1963,1970,1922</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Y65" t="n">
+        <v>4</v>
       </c>
       <c r="Z65" t="n">
         <v>154000</v>
@@ -9976,10 +9970,8 @@
           <t>23500,30550,29750</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y66" t="n">
+        <v>3</v>
       </c>
       <c r="Z66" t="n">
         <v>-1000</v>
@@ -10121,10 +10113,8 @@
           <t>1865,2085,2185,2025,2160</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y67" t="n">
+        <v>3</v>
       </c>
       <c r="Z67" t="n">
         <v>22000</v>
@@ -10176,6 +10166,731 @@
       <c r="AQ67" t="inlineStr">
         <is>
           <t>지분 싸움 및 신규 대주주 관련 논의, 단기 목표가 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-10 12:01</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>흥구석유</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>024060</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" t="n">
+        <v>14</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="L68" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="n">
+        <v>14840</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>+22.75%</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>18241859</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>267589713340</v>
+      </c>
+      <c r="R68" t="n">
+        <v>96.84</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U68" t="n">
+        <v>349</v>
+      </c>
+      <c r="V68" t="n">
+        <v>2</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>10620,10820,11230,11990,12090</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z68" t="n">
+        <v>22000</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="AD68" t="inlineStr"/>
+      <c r="AE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr"/>
+      <c r="AJ68" t="n">
+        <v>361.95</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>41</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>5307</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>36200</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>8920</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>2226</v>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>이란발 지정학적 리스크 고조에 따른 유가 급등 및 석유주 강세. 호르무즈 해협 관련 뉴스.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-10 12:01</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>2</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>흥아해운</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>003280</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" t="n">
+        <v>14</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="L69" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="n">
+        <v>1939</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>+10.17%</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>88193161</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>177862304885</v>
+      </c>
+      <c r="R69" t="n">
+        <v>103.16</v>
+      </c>
+      <c r="S69" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="U69" t="n">
+        <v>116</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1</v>
+      </c>
+      <c r="W69" t="n">
+        <v>1</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>1699,1724,1739,1760,1760</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z69" t="n">
+        <v>-706000</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr"/>
+      <c r="AJ69" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>127</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>1062</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>4795</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>1524</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>4662</v>
+      </c>
+      <c r="AQ69" t="inlineStr">
+        <is>
+          <t>외인 매수세 유입에도 불구하고 단기 차익 실현 매물 출회 가능성. 120일선 돌파 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-10 12:01</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>3</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" t="n">
+        <v>14</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="L70" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="n">
+        <v>1853000</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>-0.16%</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>1766988</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>3261852786500</v>
+      </c>
+      <c r="R70" t="n">
+        <v>91.08</v>
+      </c>
+      <c r="S70" t="n">
+        <v>50.67</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U70" t="n">
+        <v>795</v>
+      </c>
+      <c r="V70" t="n">
+        <v>68</v>
+      </c>
+      <c r="W70" t="n">
+        <v>1</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>1596000,1647000,1783000,1793000,1856000</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z70" t="n">
+        <v>-110000</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>-78000</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE70" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>-19.04</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="inlineStr"/>
+      <c r="AJ70" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>293000</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>13536024</v>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>연기금 리밸런싱 및 외국인 수급 개선에 따른 대세 상승 기대. 200만 목표.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-10 12:01</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>4</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>엔에이치스팩34호</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0197V0</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" t="n">
+        <v>14</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="L71" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="n">
+        <v>4615</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>+130.75%</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>119938155</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>597182634152</v>
+      </c>
+      <c r="R71" t="n">
+        <v>86.23999999999999</v>
+      </c>
+      <c r="S71" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>332</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
+      <c r="W71" t="n">
+        <v>1</v>
+      </c>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z71" t="n">
+        <v>-149000</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>-2304000</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>999</v>
+      </c>
+      <c r="AD71" t="inlineStr"/>
+      <c r="AE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr"/>
+      <c r="AJ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>5700</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>418</v>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>합병 대상 업종 신재생에너지 관련 기대감 속 급등. 과도한 욕심 경계.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-10 12:01</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>5</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>강동씨앤엘</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>198440</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>14</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="L72" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="n">
+        <v>2085</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>8368633</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>18416516168</v>
+      </c>
+      <c r="R72" t="n">
+        <v>78.44</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="U72" t="n">
+        <v>115</v>
+      </c>
+      <c r="V72" t="n">
+        <v>3</v>
+      </c>
+      <c r="W72" t="n">
+        <v>1</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>2095,1963,1970,1922,2085</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z72" t="n">
+        <v>-175000</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>-6.81</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>227.6</v>
+      </c>
+      <c r="AD72" t="inlineStr"/>
+      <c r="AE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr"/>
+      <c r="AJ72" t="n">
+        <v>-12.56</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>-166</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>2206</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>2930</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>910</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>1270</v>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>주요 사업 관련 소식과 함께 기타 법인 및 외국인 순매수세 유입. 주가 바닥 다지기 및 추가 상승 기대.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ72"/>
+  <dimension ref="A1:AQ77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10256,10 +10256,8 @@
           <t>10620,10820,11230,11990,12090</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y68" t="n">
+        <v>8</v>
       </c>
       <c r="Z68" t="n">
         <v>22000</v>
@@ -10401,10 +10399,8 @@
           <t>1699,1724,1739,1760,1760</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y69" t="n">
+        <v>3</v>
       </c>
       <c r="Z69" t="n">
         <v>-706000</v>
@@ -10546,10 +10542,8 @@
           <t>1596000,1647000,1783000,1793000,1856000</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y70" t="n">
+        <v>7</v>
       </c>
       <c r="Z70" t="n">
         <v>-110000</v>
@@ -10691,10 +10685,8 @@
         <v>1</v>
       </c>
       <c r="X71" t="inlineStr"/>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y71" t="n">
+        <v>2</v>
       </c>
       <c r="Z71" t="n">
         <v>-149000</v>
@@ -10836,10 +10828,8 @@
           <t>2095,1963,1970,1922,2085</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y72" t="n">
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
         <v>-175000</v>
@@ -10891,6 +10881,743 @@
       <c r="AQ72" t="inlineStr">
         <is>
           <t>주요 사업 관련 소식과 함께 기타 법인 및 외국인 순매수세 유입. 주가 바닥 다지기 및 추가 상승 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-10 15:01</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>금호타이어</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>073240</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" t="n">
+        <v>40</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="L73" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="n">
+        <v>7760</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>+7.18%</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>3815018</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>28241000000</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="T73" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="U73" t="n">
+        <v>233</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1</v>
+      </c>
+      <c r="W73" t="n">
+        <v>1</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>7120,7180,7350,7240,7100</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>999</v>
+      </c>
+      <c r="AD73" t="inlineStr"/>
+      <c r="AE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>신용 등급 상향 및 사업 정상화 기대감, 공매도와의 대결 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-10 15:01</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>2</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>SK이노베이션</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>096770</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" t="n">
+        <v>40</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="L74" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="n">
+        <v>153500</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>+11.23%</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U74" t="n">
+        <v>437</v>
+      </c>
+      <c r="V74" t="n">
+        <v>1</v>
+      </c>
+      <c r="W74" t="n">
+        <v>1</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>130800,138300,137900,138000,153500</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>999</v>
+      </c>
+      <c r="AD74" t="inlineStr"/>
+      <c r="AE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr"/>
+      <c r="AJ74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>유가 폭등으로 인한 기대감과 프로그램 매수세가 있으나, 원유 관련 주가 상승에 대한 의구심과 주가 하락 패턴에 대한 우려도 공존.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-10 15:01</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>3</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>삼미금속</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>012210</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>40</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="L75" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="n">
+        <v>13030</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>+29.91%</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="T75" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="U75" t="n">
+        <v>123</v>
+      </c>
+      <c r="V75" t="n">
+        <v>4</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>8340,8350,10200,10030,13030</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr"/>
+      <c r="AJ75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>삼미금속, 창사 이래 최대 호재 언급 있으나 구체적인 근거 제시 부족. 그래핀 신소재 관련 기대감 일부 포함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-10 15:01</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>4</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" t="n">
+        <v>40</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="L76" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="n">
+        <v>14680</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>+7.15%</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>7585059</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>110040000000</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U76" t="n">
+        <v>169</v>
+      </c>
+      <c r="V76" t="n">
+        <v>12</v>
+      </c>
+      <c r="W76" t="n">
+        <v>1</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>12850,13010,13470,13700,14960</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>-27.86</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>155.22</v>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr"/>
+      <c r="AJ76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>미국 광통신주 강세 및 외국인 수급 유입에 따른 주가 상승 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-10 15:01</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>5</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" t="n">
+        <v>40</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="L77" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="n">
+        <v>91700</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>+2.46%</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U77" t="n">
+        <v>289</v>
+      </c>
+      <c r="V77" t="n">
+        <v>12</v>
+      </c>
+      <c r="W77" t="n">
+        <v>1</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>79200,79200,87900,89500,91700</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>136.43</v>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr"/>
+      <c r="AJ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>두산에너빌리티, 웨스팅하우스 지분 인수 및 미국 원전 8기 건설 '팀코리아' 관련 대형 호재 언급. JP모건 리포트 등 일부 근거 제시.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ77"/>
+  <dimension ref="A1:AQ82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10971,10 +10971,8 @@
           <t>7120,7180,7350,7240,7100</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y73" t="n">
+        <v>5</v>
       </c>
       <c r="Z73" t="n">
         <v>0</v>
@@ -11116,10 +11114,8 @@
           <t>130800,138300,137900,138000,153500</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y74" t="n">
+        <v>2</v>
       </c>
       <c r="Z74" t="n">
         <v>0</v>
@@ -11261,10 +11257,8 @@
           <t>8340,8350,10200,10030,13030</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y75" t="n">
+        <v>2</v>
       </c>
       <c r="Z75" t="n">
         <v>0</v>
@@ -11410,10 +11404,8 @@
           <t>12850,13010,13470,13700,14960</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y76" t="n">
+        <v>5</v>
       </c>
       <c r="Z76" t="n">
         <v>0</v>
@@ -11559,10 +11551,8 @@
           <t>79200,79200,87900,89500,91700</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y77" t="n">
+        <v>7</v>
       </c>
       <c r="Z77" t="n">
         <v>0</v>
@@ -11618,6 +11608,747 @@
       <c r="AQ77" t="inlineStr">
         <is>
           <t>두산에너빌리티, 웨스팅하우스 지분 인수 및 미국 원전 8기 건설 '팀코리아' 관련 대형 호재 언급. JP모건 리포트 등 일부 근거 제시.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-11 12:01</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>삼화콘덴서</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>001820</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" t="n">
+        <v>35</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="n">
+        <v>138500</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>+19.09%</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>3120348</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>427067000000</v>
+      </c>
+      <c r="R78" t="n">
+        <v>104.02</v>
+      </c>
+      <c r="S78" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="T78" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="U78" t="n">
+        <v>110</v>
+      </c>
+      <c r="V78" t="n">
+        <v>1</v>
+      </c>
+      <c r="W78" t="n">
+        <v>0.6931930938678309</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>109800,116700,111700,116300,115700</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z78" t="n">
+        <v>52000</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>96000</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>23.03</v>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE78" t="n">
+        <v>127000</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr"/>
+      <c r="AJ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>애플 관련 호재에 따른 주가 상승 기대감. 거래량 부진 및 손바뀜 현상 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-11 12:01</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>2</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" t="n">
+        <v>35</v>
+      </c>
+      <c r="K79" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="n">
+        <v>90000</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>+0.11%</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>1296114</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>116504993250</v>
+      </c>
+      <c r="R79" t="n">
+        <v>109.42</v>
+      </c>
+      <c r="S79" t="n">
+        <v>23.59</v>
+      </c>
+      <c r="T79" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="U79" t="n">
+        <v>192</v>
+      </c>
+      <c r="V79" t="n">
+        <v>13</v>
+      </c>
+      <c r="W79" t="n">
+        <v>1.883278577788695</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>79200,87900,89500,91700,89900</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z79" t="n">
+        <v>-264000</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>26000</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>136.43</v>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr"/>
+      <c r="AJ79" t="n">
+        <v>681.8200000000001</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>132</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>12156</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>139200</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>57000</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>576505</v>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>미국 투자 협상 마무리 및 중동 에너지 공급망 이슈에 따른 두산에너빌리티의 수혜 기대. 수주 잔고 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-11 12:01</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>3</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>엑스게이트</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>356680</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" t="n">
+        <v>35</v>
+      </c>
+      <c r="K80" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="n">
+        <v>16060</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>+27.36%</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>14229867</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>207017000000</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T80" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="U80" t="n">
+        <v>130</v>
+      </c>
+      <c r="V80" t="n">
+        <v>1</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>11430,11330,11600,12610,12360</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z80" t="n">
+        <v>-71000</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>51.08</v>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr"/>
+      <c r="AJ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>젠슨 황의 AI 다음 시장으로 사이버 보안 지목에 따른 엑스게이트의 급등 기대. 양자보안 관련성 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-11 12:01</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>4</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" t="n">
+        <v>35</v>
+      </c>
+      <c r="K81" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="n">
+        <v>50400</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>-0.79%</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>100.42</v>
+      </c>
+      <c r="S81" t="n">
+        <v>38.78</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="U81" t="n">
+        <v>136</v>
+      </c>
+      <c r="V81" t="n">
+        <v>2</v>
+      </c>
+      <c r="W81" t="n">
+        <v>3.949073607894472</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>45850,48000,49150,50800,50400</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>122.37</v>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE81" t="n">
+        <v>61000</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>-17.87</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI81" t="inlineStr"/>
+      <c r="AJ81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>약 4.7조원 규모의 대규모 수주 공시 확인. 사우디 및 베트남 관련 복합 호재 기대감 형성.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-11 12:01</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>5</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>페니트리움바이오</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>187660</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="I82" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" t="n">
+        <v>35</v>
+      </c>
+      <c r="K82" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="n">
+        <v>8300</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>+11.86%</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>62.43</v>
+      </c>
+      <c r="S82" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="U82" t="n">
+        <v>170</v>
+      </c>
+      <c r="V82" t="n">
+        <v>5</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0.2244940375672235</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>5850,6470,5710,7420,8300</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>-118.31</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>330.36</v>
+      </c>
+      <c r="AD82" t="inlineStr"/>
+      <c r="AE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI82" t="inlineStr"/>
+      <c r="AJ82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>WCLC 세계폐암학회에서의 센딥 파텔 교수 데이터 발표에 따른 주가 대폭등 예고. 기술 수출 기대감.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ82"/>
+  <dimension ref="A1:AQ87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11698,10 +11698,8 @@
           <t>109800,116700,111700,116300,115700</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y78" t="n">
+        <v>3</v>
       </c>
       <c r="Z78" t="n">
         <v>52000</v>
@@ -11847,10 +11845,8 @@
           <t>79200,87900,89500,91700,89900</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y79" t="n">
+        <v>3</v>
       </c>
       <c r="Z79" t="n">
         <v>-264000</v>
@@ -11996,10 +11992,8 @@
           <t>11430,11330,11600,12610,12360</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y80" t="n">
+        <v>8</v>
       </c>
       <c r="Z80" t="n">
         <v>-71000</v>
@@ -12145,10 +12139,8 @@
           <t>45850,48000,49150,50800,50400</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y81" t="n">
+        <v>7</v>
       </c>
       <c r="Z81" t="n">
         <v>0</v>
@@ -12294,10 +12286,8 @@
           <t>5850,6470,5710,7420,8300</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y82" t="n">
+        <v>8</v>
       </c>
       <c r="Z82" t="n">
         <v>0</v>
@@ -12349,6 +12339,735 @@
       <c r="AQ82" t="inlineStr">
         <is>
           <t>WCLC 세계폐암학회에서의 센딥 파텔 교수 데이터 발표에 따른 주가 대폭등 예고. 기술 수출 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-11 15:01</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>드림시큐리티</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>203650</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="I83" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" t="n">
+        <v>42</v>
+      </c>
+      <c r="K83" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="n">
+        <v>2625</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>+23.53%</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>49199551</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>123940430128</v>
+      </c>
+      <c r="R83" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="S83" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U83" t="n">
+        <v>143</v>
+      </c>
+      <c r="V83" t="n">
+        <v>1</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0.8606155629332459</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>2025,2015,2035,2135,2125</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="Z83" t="n">
+        <v>-1952000</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>292.38</v>
+      </c>
+      <c r="AD83" t="inlineStr"/>
+      <c r="AE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI83" t="inlineStr"/>
+      <c r="AJ83" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>84</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>1244</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>4810</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>1400</v>
+      </c>
+      <c r="AP83" t="n">
+        <v>2670</v>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>개미 투자자만 많고 힘이 없는 모습, 외국인 및 법인 대량 매도 추정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-11 15:01</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>2</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>한국화장품제조</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>003350</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="I84" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" t="n">
+        <v>42</v>
+      </c>
+      <c r="K84" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="n">
+        <v>15980</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>+21.43%</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>11223555</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>174855941895</v>
+      </c>
+      <c r="R84" t="n">
+        <v>91.14</v>
+      </c>
+      <c r="S84" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="T84" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="U84" t="n">
+        <v>137</v>
+      </c>
+      <c r="V84" t="n">
+        <v>1</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0.1470098211153981</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>12750,12990,13010,13340,13160</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z84" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>115000</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD84" t="inlineStr"/>
+      <c r="AE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI84" t="inlineStr"/>
+      <c r="AJ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>61700</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>6750</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>3621</v>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>K-뷰티 대장주로서의 기대감과 함께 급등세 지속. 경영권 및 금리 인상 관련 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-11 15:01</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>3</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" t="n">
+        <v>42</v>
+      </c>
+      <c r="K85" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="n">
+        <v>1822000</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>-1.67%</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>2278910</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>4070626802000</v>
+      </c>
+      <c r="R85" t="n">
+        <v>100.91</v>
+      </c>
+      <c r="S85" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="T85" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="U85" t="n">
+        <v>800</v>
+      </c>
+      <c r="V85" t="n">
+        <v>69</v>
+      </c>
+      <c r="W85" t="n">
+        <v>1.46660846791794</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>1647000,1783000,1793000,1856000,1853000</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z85" t="n">
+        <v>-393000</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>-178000</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD85" t="inlineStr"/>
+      <c r="AE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr"/>
+      <c r="AJ85" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>305500</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>13309571</v>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>기관 매수세와 계단식 상승 기대, 중동 평화 회담 및 CPI 발표 변수 고려.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-11 15:01</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>4</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" t="n">
+        <v>42</v>
+      </c>
+      <c r="K86" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="n">
+        <v>19980</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>+1.16%</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>7092914</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>139560601095</v>
+      </c>
+      <c r="R86" t="n">
+        <v>90.22</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U86" t="n">
+        <v>171</v>
+      </c>
+      <c r="V86" t="n">
+        <v>14</v>
+      </c>
+      <c r="W86" t="n">
+        <v>4.325652732201455</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>16850,18410,19970,19450,19750</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z86" t="n">
+        <v>28000</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>-43000</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>-14.26</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>266.54</v>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE86" t="n">
+        <v>22000</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>-10.91</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI86" t="inlineStr"/>
+      <c r="AJ86" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="AK86" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>-2195</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>8148</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>40350</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>3320</v>
+      </c>
+      <c r="AP86" t="n">
+        <v>82099</v>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>대차해지 요청과 함께 공매도 관련 논의가 활발하며, 목표가 상향 및 원전 투자 관련 뉴스가 언급됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-11 15:01</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>5</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>흥구석유</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>024060</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="I87" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" t="n">
+        <v>42</v>
+      </c>
+      <c r="K87" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="n">
+        <v>14770</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>+1.79%</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>13375156</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>213914931155</v>
+      </c>
+      <c r="R87" t="n">
+        <v>73.77</v>
+      </c>
+      <c r="S87" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T87" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="U87" t="n">
+        <v>489</v>
+      </c>
+      <c r="V87" t="n">
+        <v>3</v>
+      </c>
+      <c r="W87" t="n">
+        <v>0.4753516497962403</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>10820,11230,11990,12090,14510</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z87" t="n">
+        <v>-339000</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="AD87" t="inlineStr"/>
+      <c r="AE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI87" t="inlineStr"/>
+      <c r="AJ87" t="n">
+        <v>360.24</v>
+      </c>
+      <c r="AK87" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AL87" t="n">
+        <v>41</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>5307</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>36200</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>8920</v>
+      </c>
+      <c r="AP87" t="n">
+        <v>2216</v>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>중동 전쟁 및 국제 유가 급등에 따른 전쟁 테마주로 급등. WTI 100달러 돌파 및 3연상 기대.</t>
         </is>
       </c>
     </row>
